--- a/apps/team-builder/Cool_Hollow_Coaching_Milestone_7_Team_Builder_Template.xlsx
+++ b/apps/team-builder/Cool_Hollow_Coaching_Milestone_7_Team_Builder_Template.xlsx
@@ -36,17 +36,17 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00E8C766"/>
       <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000E4643"/>
+      <color rgb="001A1A1A"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="000E4643"/>
+      <color rgb="001A1A1A"/>
       <sz val="11"/>
     </font>
     <font>
@@ -57,7 +57,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000E4643"/>
+      <color rgb="001A1A1A"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -75,11 +75,11 @@
       <name val="Calibri"/>
       <b val="1"/>
       <i val="1"/>
-      <color rgb="000E4643"/>
+      <color rgb="001A1A1A"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -88,12 +88,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E4643"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00589BA8"/>
+        <fgColor rgb="001A1A1A"/>
       </patternFill>
     </fill>
     <fill>
@@ -103,12 +98,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00B4D351"/>
+        <fgColor rgb="00E8C766"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAF8F3"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -150,19 +145,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>

--- a/apps/team-builder/Cool_Hollow_Coaching_Milestone_7_Team_Builder_Template.xlsx
+++ b/apps/team-builder/Cool_Hollow_Coaching_Milestone_7_Team_Builder_Template.xlsx
@@ -8,8 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Roles" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Candidates" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Examples" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Starter Ideas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Roles" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Candidates" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,12 +42,32 @@
       <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="001A1A1A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="005A5A5A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="001A1A1A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="11"/>
     </font>
@@ -62,21 +84,8 @@
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="005A5A5A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
       <color rgb="006B6B6B"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <i val="1"/>
-      <color rgb="001A1A1A"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -93,12 +102,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EFEFEF"/>
+        <fgColor rgb="00E8C766"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8C766"/>
+        <fgColor rgb="00EFEFEF"/>
       </patternFill>
     </fill>
     <fill>
@@ -133,11 +142,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -145,19 +155,29 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -520,10 +540,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001A1A1A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -536,161 +557,200 @@
           <t>Cool Hollow Coaching · Business Without You</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Milestone 7: Build the Team That Builds the Business</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>How to use this template</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>This template has two tabs. Fill in your role inventory and delegation map on the first tab. If you're actively hiring, fill in your candidate list on the second tab, using the exact same Role Name as the first tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="6" ht="68" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Two data tabs. Fill in your role inventory and delegation map on the Roles tab. If you're actively hiring, fill in the Candidates tab too, using the exact same Role Name as the Roles tab. Then upload this same file into each upload box in the tool, each box automatically reads the tab it needs. The Starter Ideas tab lists the roles most owner-run businesses need, check yours against it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Three steps: fill in the data tab(s), save this file, then upload this same file into the tool. The Examples and Starter Ideas tabs are for reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>The tool never reads them, only type your real data on the data tab(s).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>On the "Roles" tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>What to put here</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Role Name</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>One row per role in your inventory.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Current Delegation Level</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>1 to 5. How much of this role you still personally hold today.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>1 to 5. How much of this role you still personally hold today. 1 means it's all you, 5 means fully handed off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Target Delegation Level</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>1 to 5. How much of this role should be delegated.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Key Outcome 1, 2, 3</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>What this role owns, not just what it does day to day.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Decision Rights</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>What this role can decide without coming back to you.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Success Metric</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>How you'll know this role is working.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>On the "Candidates" tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>What to put here</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>Candidate Name</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>One row per candidate being considered.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>One row per candidate being considered. This tab is optional, only fill it if you're actively hiring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>Role Name</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Must match a Role Name on the Roles tab exactly.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Ownership, Communication, Judgment, Coachability, Results Track Record</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Each rated 1 to 5.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Fill in the data tab, save the file, then upload it straight into the tool.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="7">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -699,10 +759,408 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="006B6B6B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cool Hollow Coaching · Business Without You</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Milestone 7: Build the Team That Builds the Business</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Filled-in examples, for reference only. Type your own data on the data tab(s), not here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>The tool never reads this tab, anything you type here is ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Example for the "Roles" tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Role Name</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Current Delegation Level</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Target Delegation Level</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Key Outcome 1</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Key Outcome 2</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Key Outcome 3</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>Decision Rights</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Success Metric</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Operations Manager</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Keeps delivery on schedule across all active clients</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Owns vendor relationships and renewals</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Runs the weekly team check-in</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>Can approve spend up to $2000 without sign-off</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>On-time delivery rate at or above 95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Example for the "Candidates" tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Candidate Name</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Role Name</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Coachability</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>Results Track Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Jordan Reyes</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Operations Manager</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Sam Whitfield</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Operations Manager</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A6:H6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00E8C766"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cool Hollow Coaching · Business Without You</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Milestone 7: Build the Team That Builds the Business</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>The most common answers we see across owner-run businesses. Copy any that are true for yours onto the data tab, reworded to match how your business actually runs, then fill in the numbers and ratings yourself, honestly. Don't copy anything that isn't real for you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>The tool never reads this tab, copy items onto the data tab to use them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Roles most owner-run businesses need</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Operations Manager (keeps delivery running without you)</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Office Manager / Admin (paperwork, scheduling, phones)</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Bookkeeper / Finance Lead (invoices, bills, payroll, reports)</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Sales Lead (quotes, follow-ups, closing)</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Service or Delivery Lead (quality and dispatch on the ground)</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Field Supervisor / Crew Lead (runs the team day to day)</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Customer Service Lead (owns the inbox and the phone)</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Marketing Coordinator (content, ads, and the pipeline top)</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>HR / Hiring Coordinator (job posts, screening, onboarding)</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A6:B6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C8A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -721,464 +1179,482 @@
           <t>Cool Hollow Coaching · Business Without You</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Milestone 7: Build the Team That Builds the Business</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Role Name</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Current Delegation Level</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Target Delegation Level</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Key Outcome 1</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Key Outcome 2</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Key Outcome 3</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>Decision Rights</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>Success Metric</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Operations Manager</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>Keeps delivery on schedule across all active clients</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>Owns vendor relationships and renewals</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>Runs the weekly team check-in</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>Can approve spend up to $2000 without sign-off</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>On-time delivery rate at or above 95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Your data starts here, replace or delete the example rows above</t>
-        </is>
-      </c>
+      <c r="A5" s="15" t="n"/>
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="15" t="n"/>
+      <c r="E5" s="15" t="n"/>
+      <c r="F5" s="15" t="n"/>
+      <c r="G5" s="15" t="n"/>
+      <c r="H5" s="15" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="n"/>
+      <c r="B6" s="16" t="n"/>
+      <c r="C6" s="16" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="n"/>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n"/>
+      <c r="A7" s="15" t="n"/>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="15" t="n"/>
+      <c r="E7" s="15" t="n"/>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n"/>
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="15" t="n"/>
+      <c r="H8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n"/>
+      <c r="A9" s="15" t="n"/>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="15" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="11" t="n"/>
+      <c r="A10" s="15" t="n"/>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
+      <c r="A11" s="15" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="15" t="n"/>
+      <c r="H11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n"/>
+      <c r="A12" s="15" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="15" t="n"/>
+      <c r="H12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n"/>
+      <c r="A13" s="15" t="n"/>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="15" t="n"/>
+      <c r="F13" s="15" t="n"/>
+      <c r="G13" s="15" t="n"/>
+      <c r="H13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="11" t="n"/>
+      <c r="A14" s="15" t="n"/>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="15" t="n"/>
+      <c r="H14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
+      <c r="A15" s="15" t="n"/>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="15" t="n"/>
+      <c r="G15" s="15" t="n"/>
+      <c r="H15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
-      <c r="H16" s="11" t="n"/>
+      <c r="A16" s="15" t="n"/>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="15" t="n"/>
+      <c r="H16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="n"/>
+      <c r="A17" s="15" t="n"/>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="15" t="n"/>
+      <c r="H17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="n"/>
+      <c r="A18" s="15" t="n"/>
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="15" t="n"/>
+      <c r="H18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="11" t="n"/>
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="15" t="n"/>
+      <c r="H19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
-      <c r="H20" s="11" t="n"/>
+      <c r="A20" s="15" t="n"/>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="15" t="n"/>
+      <c r="H20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="n"/>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="n"/>
+      <c r="A21" s="15" t="n"/>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="15" t="n"/>
+      <c r="H21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
-      <c r="H22" s="11" t="n"/>
+      <c r="A22" s="15" t="n"/>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="15" t="n"/>
+      <c r="H22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="11" t="n"/>
+      <c r="A23" s="15" t="n"/>
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="15" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="15" t="n"/>
+      <c r="G23" s="15" t="n"/>
+      <c r="H23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
-      <c r="H24" s="11" t="n"/>
+      <c r="A24" s="15" t="n"/>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="15" t="n"/>
+      <c r="H24" s="15" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n"/>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="11" t="n"/>
-      <c r="G25" s="11" t="n"/>
-      <c r="H25" s="11" t="n"/>
+      <c r="A25" s="15" t="n"/>
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="15" t="n"/>
+      <c r="E25" s="15" t="n"/>
+      <c r="F25" s="15" t="n"/>
+      <c r="G25" s="15" t="n"/>
+      <c r="H25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n"/>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
-      <c r="H26" s="11" t="n"/>
+      <c r="A26" s="15" t="n"/>
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="15" t="n"/>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="15" t="n"/>
+      <c r="H26" s="15" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n"/>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="11" t="n"/>
-      <c r="G27" s="11" t="n"/>
-      <c r="H27" s="11" t="n"/>
+      <c r="A27" s="15" t="n"/>
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="16" t="n"/>
+      <c r="D27" s="15" t="n"/>
+      <c r="E27" s="15" t="n"/>
+      <c r="F27" s="15" t="n"/>
+      <c r="G27" s="15" t="n"/>
+      <c r="H27" s="15" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n"/>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="11" t="n"/>
-      <c r="G28" s="11" t="n"/>
-      <c r="H28" s="11" t="n"/>
+      <c r="A28" s="15" t="n"/>
+      <c r="B28" s="16" t="n"/>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="15" t="n"/>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="15" t="n"/>
+      <c r="H28" s="15" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n"/>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="11" t="n"/>
-      <c r="G29" s="11" t="n"/>
-      <c r="H29" s="11" t="n"/>
+      <c r="A29" s="15" t="n"/>
+      <c r="B29" s="16" t="n"/>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="15" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="15" t="n"/>
+      <c r="H29" s="15" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="n"/>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="11" t="n"/>
-      <c r="F30" s="11" t="n"/>
-      <c r="G30" s="11" t="n"/>
-      <c r="H30" s="11" t="n"/>
+      <c r="A30" s="15" t="n"/>
+      <c r="B30" s="16" t="n"/>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="15" t="n"/>
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="15" t="n"/>
+      <c r="H30" s="15" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n"/>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="11" t="n"/>
-      <c r="F31" s="11" t="n"/>
-      <c r="G31" s="11" t="n"/>
-      <c r="H31" s="11" t="n"/>
+      <c r="A31" s="15" t="n"/>
+      <c r="B31" s="16" t="n"/>
+      <c r="C31" s="16" t="n"/>
+      <c r="D31" s="15" t="n"/>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="15" t="n"/>
+      <c r="H31" s="15" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="n"/>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="11" t="n"/>
-      <c r="F32" s="11" t="n"/>
-      <c r="G32" s="11" t="n"/>
-      <c r="H32" s="11" t="n"/>
+      <c r="A32" s="15" t="n"/>
+      <c r="B32" s="16" t="n"/>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="15" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="15" t="n"/>
+      <c r="H32" s="15" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n"/>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="11" t="n"/>
-      <c r="F33" s="11" t="n"/>
-      <c r="G33" s="11" t="n"/>
-      <c r="H33" s="11" t="n"/>
+      <c r="A33" s="15" t="n"/>
+      <c r="B33" s="16" t="n"/>
+      <c r="C33" s="16" t="n"/>
+      <c r="D33" s="15" t="n"/>
+      <c r="E33" s="15" t="n"/>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="15" t="n"/>
+      <c r="H33" s="15" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="n"/>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="11" t="n"/>
-      <c r="F34" s="11" t="n"/>
-      <c r="G34" s="11" t="n"/>
-      <c r="H34" s="11" t="n"/>
+      <c r="A34" s="15" t="n"/>
+      <c r="B34" s="16" t="n"/>
+      <c r="C34" s="16" t="n"/>
+      <c r="D34" s="15" t="n"/>
+      <c r="E34" s="15" t="n"/>
+      <c r="F34" s="15" t="n"/>
+      <c r="G34" s="15" t="n"/>
+      <c r="H34" s="15" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="n"/>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="11" t="n"/>
-      <c r="E35" s="11" t="n"/>
-      <c r="F35" s="11" t="n"/>
-      <c r="G35" s="11" t="n"/>
-      <c r="H35" s="11" t="n"/>
+      <c r="A35" s="15" t="n"/>
+      <c r="B35" s="16" t="n"/>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="15" t="n"/>
+      <c r="E35" s="15" t="n"/>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="15" t="n"/>
+      <c r="H35" s="15" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="n"/>
-      <c r="B36" s="11" t="n"/>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="11" t="n"/>
-      <c r="F36" s="11" t="n"/>
-      <c r="G36" s="11" t="n"/>
-      <c r="H36" s="11" t="n"/>
+      <c r="A36" s="15" t="n"/>
+      <c r="B36" s="16" t="n"/>
+      <c r="C36" s="16" t="n"/>
+      <c r="D36" s="15" t="n"/>
+      <c r="E36" s="15" t="n"/>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="15" t="n"/>
+      <c r="H36" s="15" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="n"/>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="11" t="n"/>
-      <c r="G37" s="11" t="n"/>
-      <c r="H37" s="11" t="n"/>
+      <c r="A37" s="15" t="n"/>
+      <c r="B37" s="16" t="n"/>
+      <c r="C37" s="16" t="n"/>
+      <c r="D37" s="15" t="n"/>
+      <c r="E37" s="15" t="n"/>
+      <c r="F37" s="15" t="n"/>
+      <c r="G37" s="15" t="n"/>
+      <c r="H37" s="15" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="n"/>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="11" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="11" t="n"/>
-      <c r="F38" s="11" t="n"/>
-      <c r="G38" s="11" t="n"/>
-      <c r="H38" s="11" t="n"/>
+      <c r="A38" s="15" t="n"/>
+      <c r="B38" s="16" t="n"/>
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="15" t="n"/>
+      <c r="E38" s="15" t="n"/>
+      <c r="F38" s="15" t="n"/>
+      <c r="G38" s="15" t="n"/>
+      <c r="H38" s="15" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="n"/>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="11" t="n"/>
-      <c r="F39" s="11" t="n"/>
-      <c r="G39" s="11" t="n"/>
-      <c r="H39" s="11" t="n"/>
+      <c r="A39" s="15" t="n"/>
+      <c r="B39" s="16" t="n"/>
+      <c r="C39" s="16" t="n"/>
+      <c r="D39" s="15" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="15" t="n"/>
+      <c r="H39" s="15" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="n"/>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="11" t="n"/>
-      <c r="F40" s="11" t="n"/>
-      <c r="G40" s="11" t="n"/>
-      <c r="H40" s="11" t="n"/>
+      <c r="A40" s="15" t="n"/>
+      <c r="B40" s="16" t="n"/>
+      <c r="C40" s="16" t="n"/>
+      <c r="D40" s="15" t="n"/>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="15" t="n"/>
+      <c r="G40" s="15" t="n"/>
+      <c r="H40" s="15" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="n"/>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="11" t="n"/>
-      <c r="G41" s="11" t="n"/>
-      <c r="H41" s="11" t="n"/>
+      <c r="A41" s="15" t="n"/>
+      <c r="B41" s="16" t="n"/>
+      <c r="C41" s="16" t="n"/>
+      <c r="D41" s="15" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="15" t="n"/>
+      <c r="G41" s="15" t="n"/>
+      <c r="H41" s="15" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="n"/>
+      <c r="B42" s="16" t="n"/>
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="15" t="n"/>
+      <c r="E42" s="15" t="n"/>
+      <c r="F42" s="15" t="n"/>
+      <c r="G42" s="15" t="n"/>
+      <c r="H42" s="15" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="n"/>
+      <c r="B43" s="16" t="n"/>
+      <c r="C43" s="16" t="n"/>
+      <c r="D43" s="15" t="n"/>
+      <c r="E43" s="15" t="n"/>
+      <c r="F43" s="15" t="n"/>
+      <c r="G43" s="15" t="n"/>
+      <c r="H43" s="15" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="n"/>
+      <c r="B44" s="16" t="n"/>
+      <c r="C44" s="16" t="n"/>
+      <c r="D44" s="15" t="n"/>
+      <c r="E44" s="15" t="n"/>
+      <c r="F44" s="15" t="n"/>
+      <c r="G44" s="15" t="n"/>
+      <c r="H44" s="15" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A6:H6"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="B7:B41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." type="whole" operator="between">
+    <dataValidation sqref="B5:B44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." promptTitle="Rate 1 to 5" prompt="1 means it's all you, 5 means fully handed off" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation sqref="C7:C41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." type="whole" operator="between">
+    <dataValidation sqref="C5:C44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." promptTitle="Rate 1 to 5" prompt="Where this role's delegation should get to" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
@@ -1187,13 +1663,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C8A227"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1211,425 +1688,447 @@
           <t>Cool Hollow Coaching · Business Without You</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Milestone 7: Build the Team That Builds the Business</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Candidate Name</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Role Name</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Ownership</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Judgment</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Coachability</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>Results Track Record</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Jordan Reyes</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Operations Manager</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Your data starts here, replace or delete the example rows above</t>
-        </is>
-      </c>
+      <c r="A5" s="15" t="n"/>
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="16" t="n"/>
+      <c r="G5" s="16" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="n"/>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="16" t="n"/>
+      <c r="D6" s="16" t="n"/>
+      <c r="E6" s="16" t="n"/>
+      <c r="F6" s="16" t="n"/>
+      <c r="G6" s="16" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="n"/>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="11" t="n"/>
+      <c r="A7" s="15" t="n"/>
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="16" t="n"/>
+      <c r="G7" s="16" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="16" t="n"/>
+      <c r="G8" s="16" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
+      <c r="A9" s="15" t="n"/>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="16" t="n"/>
+      <c r="F9" s="16" t="n"/>
+      <c r="G9" s="16" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
+      <c r="A10" s="15" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
+      <c r="G10" s="16" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
+      <c r="A11" s="15" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
+      <c r="G11" s="16" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
+      <c r="A12" s="15" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
+      <c r="G12" s="16" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
+      <c r="A13" s="15" t="n"/>
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="16" t="n"/>
+      <c r="G13" s="16" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
+      <c r="A14" s="15" t="n"/>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="16" t="n"/>
+      <c r="G14" s="16" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
+      <c r="A15" s="15" t="n"/>
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="16" t="n"/>
+      <c r="G15" s="16" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
+      <c r="A16" s="15" t="n"/>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="16" t="n"/>
+      <c r="G16" s="16" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="11" t="n"/>
+      <c r="A17" s="15" t="n"/>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
+      <c r="G17" s="16" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
+      <c r="A18" s="15" t="n"/>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="16" t="n"/>
+      <c r="G18" s="16" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="11" t="n"/>
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="16" t="n"/>
+      <c r="F19" s="16" t="n"/>
+      <c r="G19" s="16" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
+      <c r="A20" s="15" t="n"/>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="16" t="n"/>
+      <c r="G20" s="16" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="n"/>
-      <c r="G21" s="11" t="n"/>
+      <c r="A21" s="15" t="n"/>
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="16" t="n"/>
+      <c r="G21" s="16" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
+      <c r="A22" s="15" t="n"/>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="16" t="n"/>
+      <c r="G22" s="16" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="11" t="n"/>
+      <c r="A23" s="15" t="n"/>
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="16" t="n"/>
+      <c r="F23" s="16" t="n"/>
+      <c r="G23" s="16" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
+      <c r="A24" s="15" t="n"/>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="16" t="n"/>
+      <c r="G24" s="16" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n"/>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="11" t="n"/>
-      <c r="G25" s="11" t="n"/>
+      <c r="A25" s="15" t="n"/>
+      <c r="B25" s="15" t="n"/>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="16" t="n"/>
+      <c r="G25" s="16" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n"/>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
+      <c r="A26" s="15" t="n"/>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="16" t="n"/>
+      <c r="F26" s="16" t="n"/>
+      <c r="G26" s="16" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n"/>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="11" t="n"/>
-      <c r="G27" s="11" t="n"/>
+      <c r="A27" s="15" t="n"/>
+      <c r="B27" s="15" t="n"/>
+      <c r="C27" s="16" t="n"/>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="16" t="n"/>
+      <c r="F27" s="16" t="n"/>
+      <c r="G27" s="16" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n"/>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="11" t="n"/>
-      <c r="G28" s="11" t="n"/>
+      <c r="A28" s="15" t="n"/>
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="16" t="n"/>
+      <c r="F28" s="16" t="n"/>
+      <c r="G28" s="16" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n"/>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="11" t="n"/>
-      <c r="G29" s="11" t="n"/>
+      <c r="A29" s="15" t="n"/>
+      <c r="B29" s="15" t="n"/>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="16" t="n"/>
+      <c r="F29" s="16" t="n"/>
+      <c r="G29" s="16" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="n"/>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="11" t="n"/>
-      <c r="F30" s="11" t="n"/>
-      <c r="G30" s="11" t="n"/>
+      <c r="A30" s="15" t="n"/>
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="16" t="n"/>
+      <c r="G30" s="16" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n"/>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="11" t="n"/>
-      <c r="F31" s="11" t="n"/>
-      <c r="G31" s="11" t="n"/>
+      <c r="A31" s="15" t="n"/>
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="16" t="n"/>
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="16" t="n"/>
+      <c r="G31" s="16" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="n"/>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="11" t="n"/>
-      <c r="F32" s="11" t="n"/>
-      <c r="G32" s="11" t="n"/>
+      <c r="A32" s="15" t="n"/>
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="n"/>
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="16" t="n"/>
+      <c r="G32" s="16" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n"/>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="11" t="n"/>
-      <c r="F33" s="11" t="n"/>
-      <c r="G33" s="11" t="n"/>
+      <c r="A33" s="15" t="n"/>
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="16" t="n"/>
+      <c r="D33" s="16" t="n"/>
+      <c r="E33" s="16" t="n"/>
+      <c r="F33" s="16" t="n"/>
+      <c r="G33" s="16" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="n"/>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="11" t="n"/>
-      <c r="F34" s="11" t="n"/>
-      <c r="G34" s="11" t="n"/>
+      <c r="A34" s="15" t="n"/>
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="16" t="n"/>
+      <c r="D34" s="16" t="n"/>
+      <c r="E34" s="16" t="n"/>
+      <c r="F34" s="16" t="n"/>
+      <c r="G34" s="16" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="n"/>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="11" t="n"/>
-      <c r="E35" s="11" t="n"/>
-      <c r="F35" s="11" t="n"/>
-      <c r="G35" s="11" t="n"/>
+      <c r="A35" s="15" t="n"/>
+      <c r="B35" s="15" t="n"/>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="16" t="n"/>
+      <c r="E35" s="16" t="n"/>
+      <c r="F35" s="16" t="n"/>
+      <c r="G35" s="16" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="n"/>
-      <c r="B36" s="11" t="n"/>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="11" t="n"/>
-      <c r="F36" s="11" t="n"/>
-      <c r="G36" s="11" t="n"/>
+      <c r="A36" s="15" t="n"/>
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="16" t="n"/>
+      <c r="D36" s="16" t="n"/>
+      <c r="E36" s="16" t="n"/>
+      <c r="F36" s="16" t="n"/>
+      <c r="G36" s="16" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="n"/>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="11" t="n"/>
-      <c r="G37" s="11" t="n"/>
+      <c r="A37" s="15" t="n"/>
+      <c r="B37" s="15" t="n"/>
+      <c r="C37" s="16" t="n"/>
+      <c r="D37" s="16" t="n"/>
+      <c r="E37" s="16" t="n"/>
+      <c r="F37" s="16" t="n"/>
+      <c r="G37" s="16" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="n"/>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="11" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="11" t="n"/>
-      <c r="F38" s="11" t="n"/>
-      <c r="G38" s="11" t="n"/>
+      <c r="A38" s="15" t="n"/>
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="16" t="n"/>
+      <c r="E38" s="16" t="n"/>
+      <c r="F38" s="16" t="n"/>
+      <c r="G38" s="16" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="n"/>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="11" t="n"/>
-      <c r="F39" s="11" t="n"/>
-      <c r="G39" s="11" t="n"/>
+      <c r="A39" s="15" t="n"/>
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="16" t="n"/>
+      <c r="D39" s="16" t="n"/>
+      <c r="E39" s="16" t="n"/>
+      <c r="F39" s="16" t="n"/>
+      <c r="G39" s="16" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="n"/>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="11" t="n"/>
-      <c r="F40" s="11" t="n"/>
-      <c r="G40" s="11" t="n"/>
+      <c r="A40" s="15" t="n"/>
+      <c r="B40" s="15" t="n"/>
+      <c r="C40" s="16" t="n"/>
+      <c r="D40" s="16" t="n"/>
+      <c r="E40" s="16" t="n"/>
+      <c r="F40" s="16" t="n"/>
+      <c r="G40" s="16" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="n"/>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="11" t="n"/>
-      <c r="G41" s="11" t="n"/>
+      <c r="A41" s="15" t="n"/>
+      <c r="B41" s="15" t="n"/>
+      <c r="C41" s="16" t="n"/>
+      <c r="D41" s="16" t="n"/>
+      <c r="E41" s="16" t="n"/>
+      <c r="F41" s="16" t="n"/>
+      <c r="G41" s="16" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="n"/>
+      <c r="B42" s="15" t="n"/>
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="16" t="n"/>
+      <c r="E42" s="16" t="n"/>
+      <c r="F42" s="16" t="n"/>
+      <c r="G42" s="16" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="n"/>
+      <c r="B43" s="15" t="n"/>
+      <c r="C43" s="16" t="n"/>
+      <c r="D43" s="16" t="n"/>
+      <c r="E43" s="16" t="n"/>
+      <c r="F43" s="16" t="n"/>
+      <c r="G43" s="16" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="n"/>
+      <c r="B44" s="15" t="n"/>
+      <c r="C44" s="16" t="n"/>
+      <c r="D44" s="16" t="n"/>
+      <c r="E44" s="16" t="n"/>
+      <c r="F44" s="16" t="n"/>
+      <c r="G44" s="16" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A6:G6"/>
+  <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <dataValidations count="5">
-    <dataValidation sqref="C7:C41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." type="whole" operator="between">
+    <dataValidation sqref="C5:C44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." promptTitle="Rate 1 to 5" prompt="Rate 1 to 5" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation sqref="D7:D41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." type="whole" operator="between">
+    <dataValidation sqref="D5:D44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." promptTitle="Rate 1 to 5" prompt="Rate 1 to 5" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation sqref="E7:E41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." type="whole" operator="between">
+    <dataValidation sqref="E5:E44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." promptTitle="Rate 1 to 5" prompt="Rate 1 to 5" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation sqref="F7:F41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." type="whole" operator="between">
+    <dataValidation sqref="F5:F44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." promptTitle="Rate 1 to 5" prompt="Rate 1 to 5" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation sqref="G7:G41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." type="whole" operator="between">
+    <dataValidation sqref="G5:G44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." promptTitle="Rate 1 to 5" prompt="Rate 1 to 5" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
